--- a/output/pdf_financials_xlsx/CYBT.xlsx
+++ b/output/pdf_financials_xlsx/CYBT.xlsx
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.148069</v>
+        <v>9.658758000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.028269</v>
+        <v>27.352586</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.956879</v>
+        <v>14.688743</v>
       </c>
     </row>
     <row r="93">
@@ -3264,7 +3264,11 @@
           <t>Warrant reserve (note 9 (c))</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3322,7 +3326,11 @@
           <t>Share based payment reserve (note 9 (b))</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -3984,7 +3992,11 @@
           <t>Warrant reserve (note 9 (c)) 6,518,108</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4046,7 +4058,11 @@
           <t>Share based payment reserve (note 9 (b)) 6,129,916</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4591,7 +4607,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>4.59449</v>
       </c>
@@ -4651,7 +4671,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>4.916199</v>
       </c>

--- a/output/pdf_financials_xlsx/CYBT.xlsx
+++ b/output/pdf_financials_xlsx/CYBT.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.563807</v>
+        <v>11.426901</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.33009</v>
+        <v>12.156085</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.338383</v>
+        <v>6.308796</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.441266</v>
+        <v>-10.30436</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.612854</v>
+        <v>-10.213141</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.556202</v>
+        <v>-3.414211</v>
       </c>
     </row>
     <row r="12">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">

--- a/output/pdf_financials_xlsx/CYBT.xlsx
+++ b/output/pdf_financials_xlsx/CYBT.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.678692</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>2.105134</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.293496</v>
       </c>
     </row>
     <row r="65">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.182402</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.898471</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.258337</v>
       </c>
     </row>
     <row r="68">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.194373</v>
+        <v>0.25374</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-1.260872</v>
+        <v>-1.02281</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.6698539999999999</v>
+        <v>0.703615</v>
       </c>
     </row>
     <row r="102">
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-1.069513</v>
+        <v>-1.010146</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>4.684209</v>
+        <v>4.922271</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.189556</v>
+        <v>0.223317</v>
       </c>
     </row>
     <row r="107">
@@ -5169,7 +5169,11 @@
           <t>Decrease in HST receivable</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>0.059367</v>
       </c>
@@ -6048,7 +6052,11 @@
           <t>Decrease in HST receivable 119,031</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
